--- a/data/trans_orig/IP42B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP42B-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>14256</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32765</t>
+          <t>33287</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38019</t>
+          <t>38388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22889</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24732</t>
+          <t>24445</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32366</t>
+          <t>33373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60152</t>
+          <t>60249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65308</t>
+          <t>65314</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10953</t>
+          <t>10980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46676</t>
+          <t>46321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52161</t>
+          <t>52148</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54516</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60107</t>
+          <t>60727</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103291</t>
+          <t>103264</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111472</t>
+          <t>111008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>776</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13901</t>
+          <t>13907</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17776</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23349</t>
+          <t>23278</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>28416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35906</t>
+          <t>35841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>46</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>17293</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14899</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116930</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>127198</t>
+          <t>127419</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>143116</t>
+          <t>142738</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>153102</t>
+          <t>153291</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>263655</t>
+          <t>263578</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278586</t>
+          <t>278876</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11426</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26329</t>
+          <t>25691</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31566</t>
+          <t>31553</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13827</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23031</t>
+          <t>23204</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29167</t>
+          <t>29240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>472</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>29583</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34070</t>
+          <t>34077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21919</t>
+          <t>22414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>27927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54926</t>
+          <t>53959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61766</t>
+          <t>61285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>14389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>39223</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48226</t>
+          <t>48145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57819</t>
+          <t>57279</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65728</t>
+          <t>65766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99590</t>
+          <t>100166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112524</t>
+          <t>112637</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13006</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25749</t>
+          <t>25609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33355</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42036</t>
+          <t>42006</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27875</t>
+          <t>28173</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37387</t>
+          <t>37236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65036</t>
+          <t>65176</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77779</t>
+          <t>77595</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,21%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19850</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35649</t>
+          <t>36540</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17957</t>
+          <t>17902</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34054</t>
+          <t>33282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43396</t>
+          <t>42257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64429</t>
+          <t>63283</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>138771</t>
+          <t>137880</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>154570</t>
+          <t>153620</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>148506</t>
+          <t>149278</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>164603</t>
+          <t>164658</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>292551</t>
+          <t>293697</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>313584</t>
+          <t>314723</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16858</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31827</t>
+          <t>31534</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37462</t>
+          <t>37441</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21751</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20064</t>
+          <t>20432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25003</t>
+          <t>25002</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43700</t>
+          <t>44287</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50598</t>
+          <t>50742</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>768</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19213</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>30124</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35490</t>
+          <t>35491</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52513</t>
+          <t>52881</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58945</t>
+          <t>58948</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13090</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49433</t>
+          <t>49782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56125</t>
+          <t>56189</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70065</t>
+          <t>70059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76829</t>
+          <t>76911</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123046</t>
+          <t>123176</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132189</t>
+          <t>131963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7439</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50285</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57775</t>
+          <t>57849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50663</t>
+          <t>50172</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56374</t>
+          <t>56292</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104311</t>
+          <t>103691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113297</t>
+          <t>113029</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>718</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17070</t>
+          <t>17097</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22160</t>
+          <t>21708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23971</t>
+          <t>23642</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23349</t>
+          <t>23892</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>41408</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>173865</t>
+          <t>174317</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>186369</t>
+          <t>186090</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>204221</t>
+          <t>204550</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>217193</t>
+          <t>217561</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>382491</t>
+          <t>382808</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>400867</t>
+          <t>400324</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP42B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP42B-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3485</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1479</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4673</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4514</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,81%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3476</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19007</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16222</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19707</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17450</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14256</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14415</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>18929</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,19%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>76,15%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19007</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16231</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19707</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>82,36%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>55</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33287</t>
+          <t>32774</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38388</t>
+          <t>38000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19707</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19707</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19707</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18929</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>18929</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>18929</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19707</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>19707</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>19707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4134</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1367</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4087</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4754</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>29,09%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4695</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12684</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9917</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14051</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>13667</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>12684</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9964</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>14051</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,27%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>70,91%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>39</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>22964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14051</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14051</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14051</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>13667</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>13667</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>13667</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>14051</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>14051</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>14051</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3476</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,44%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1475</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4738</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5017</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,05%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3447</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36119</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>33344</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36820</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,56%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>27708</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24445</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>24166</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>29183</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,95%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>82,81%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>36119</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>33373</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>36820</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>90,64%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>96</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60249</t>
+          <t>59974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65314</t>
+          <t>65310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>36820</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>36820</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>36820</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>29183</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>29183</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>29183</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>36820</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>36820</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>36820</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7518</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2686</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6501</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7234</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,08%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6754</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10980</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>58016</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>53904</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>60092</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>50136</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>46321</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>52148</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>45588</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>51722</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,92%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>58016</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>54668</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>60727</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103264</t>
+          <t>103398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111008</t>
+          <t>111480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>61422</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>61422</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>61422</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>52822</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>52822</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>52822</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>61422</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>61422</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>61422</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2099,67 +2099,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2789</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6577</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11,6%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>27,34%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>2859</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6212</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6561</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>19,57%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>42,51%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2789</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6356</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>11,6%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10252</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21265</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17477</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23128</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>88,4%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>72,66%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>11754</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>8401</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>13907</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>13918</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>80,43%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>57,49%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,17%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>21265</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>17698</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>23278</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>88,4%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>28568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35841</t>
+          <t>35940</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>24054</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>24054</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>24054</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>14613</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>14613</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>14613</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>24054</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>24054</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>24054</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2744</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>42,23%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2657</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4171</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4161</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>54,73%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>85,91%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1420</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3316</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -2555,67 +2555,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>1942</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>57,77%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>2198</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3641</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4210</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>45,27%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>14,09%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3362</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>57,77%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,93%</t>
         </is>
       </c>
     </row>
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>4855</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>4855</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>4855</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>3362</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>3362</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>3362</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>10385</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6182</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>16118</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>11156</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>6651</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>17293</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>6417</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>16856</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>8,32%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>10385</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>6124</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>16677</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>29725</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>149030</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>143297</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>153233</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>93,49%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>89,89%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>96,12%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>122914</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>116777</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>127419</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>117214</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>127653</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>91,68%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>87,1%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>95,04%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>149030</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>142738</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>153291</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>263578</t>
+          <t>263760</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278876</t>
+          <t>278281</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>159415</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>159415</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>159415</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>134070</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>134070</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>134070</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>159415</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>159415</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>159415</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,72 +3357,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3476</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1886</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5153</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5182</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,37%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>2,83%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>734</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -3470,74 +3470,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12178</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15654</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14693</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11426</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16109</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11397</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16110</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,63%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>68,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>68,74%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>97,17%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14986</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12254</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15654</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,73%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>78,28%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>43</t>
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25691</t>
+          <t>26322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31553</t>
+          <t>31499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15654</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15654</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15654</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>16579</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>16579</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>16579</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>15654</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>15654</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>15654</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,72 +3700,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1573</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,4%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1950</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5122</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5104</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>13,5%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1573</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -3813,72 +3813,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14478</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11493</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16051</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>12493</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9321</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13825</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9339</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>13834</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>86,5%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>64,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>14478</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>11147</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>16051</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,2%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>22875</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29240</t>
+          <t>29225</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16051</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16051</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16051</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>14443</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>14443</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>14443</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>16051</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>16051</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>16051</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,72 +4043,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3334</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6860</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1805</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4966</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4556</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3334</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1297</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6810</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -4156,74 +4156,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22364</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27910</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,59%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>32744</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29583</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>34077</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>29993</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>34075</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,77%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>86,81%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>98,63%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>25890</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>22414</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27927</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,59%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>76,7%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>95,56%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>86</t>
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53959</t>
+          <t>54406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61285</t>
+          <t>61311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>29224</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>29224</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>29224</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>34549</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>34549</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>34549</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>29224</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>29224</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>29224</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6398</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3283</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11595</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9304</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5467</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14389</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5334</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14339</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,35%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>26,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6398</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3089</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11576</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22302</t>
+          <t>22502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62457</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>57260</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>65572</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>44308</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>39223</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48145</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>39273</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>48278</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>73,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>62457</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>57279</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>65766</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,71%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100166</t>
+          <t>99966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112637</t>
+          <t>112598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>68855</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>68855</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>68855</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>53612</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>53612</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>53612</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>68855</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>68855</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>68855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10034</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5760</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15187</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>34,86%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>8854</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5214</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14307</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5244</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14135</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>18,75%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>30,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>10034</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6329</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>15392</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>23,03%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13190</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25609</t>
+          <t>25581</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>33531</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28378</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>37805</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>76,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>65,14%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>86,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>38366</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>32913</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>42006</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>33085</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>41976</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>81,25%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>69,7%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>33531</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>28173</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>37236</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>76,97%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65176</t>
+          <t>65204</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77595</t>
+          <t>77880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>43565</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>43565</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>43565</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>47220</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>47220</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>47220</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>43565</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>43565</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>43565</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5077,67 +5077,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1092</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5790</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>32,97%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>62,86%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>3716</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1398</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6027</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6506</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>46,36%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>17,44%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>75,19%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5770</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>62,98%</t>
         </is>
       </c>
     </row>
@@ -5185,72 +5185,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6174</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3421</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8119</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>67,03%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>37,14%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>88,14%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>4300</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6618</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6620</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>53,64%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>24,81%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>82,56%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>6174</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>3441</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8135</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>67,03%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>8016</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>8016</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>8016</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>9211</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>9211</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>9211</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>25044</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>17991</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>33839</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>18,54%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>27514</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>20800</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>36540</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>20414</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>36306</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>15,77%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>11,93%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>20,95%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>25044</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>17902</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>33282</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>42840</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63283</t>
+          <t>64607</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>157516</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>148721</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>164569</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>86,28%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>81,46%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>90,15%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>146906</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>137880</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>153620</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>138114</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>154006</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>84,23%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>79,05%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>88,07%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>157516</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>149278</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>164658</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>86,28%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>293697</t>
+          <t>292373</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>314723</t>
+          <t>314140</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>182560</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>182560</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>182560</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>174420</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>174420</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>174420</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>182560</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>182560</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>182560</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,72 +5992,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,62%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1707</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4775</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4581</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,82%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1466</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4627</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -6105,72 +6105,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19790</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16873</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21256</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>79,38%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15675</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12607</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16920</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12801</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16932</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>72,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19790</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16629</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21256</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31534</t>
+          <t>31949</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37441</t>
+          <t>37589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21256</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21256</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21256</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>17382</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>17382</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>17382</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21256</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21256</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21256</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6335,72 +6335,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1376</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4815</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4533</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2125</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5173</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -6448,74 +6448,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23480</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20317</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>24997</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>24983</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21544</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21826</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>26359</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>82,8%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>23480</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>20432</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>25002</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>79,8%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,65%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>71</t>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44287</t>
+          <t>44088</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50742</t>
+          <t>50602</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>25605</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>25605</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>25605</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>26359</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>26359</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>26359</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>25605</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>25605</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>25605</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6678,72 +6678,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2221</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7194</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>759</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4005</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4176</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,21%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2221</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5957</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>759</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -6791,74 +6791,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33860</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28887</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35484</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>22876</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19630</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>19459</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>23635</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,79%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>82,33%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33860</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30124</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>35491</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,84%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>83,49%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>84</t>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52881</t>
+          <t>52717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58948</t>
+          <t>58957</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>36081</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>36081</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>36081</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>23635</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>23635</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>23635</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>36081</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>36081</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>36081</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3668</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8185</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3917</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8148</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1782</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,76%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3668</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12960</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>74538</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>70021</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>76876</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>54013</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>49782</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56189</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>50110</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>56148</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,24%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>74538</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>70059</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>76911</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123176</t>
+          <t>122913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131963</t>
+          <t>131977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>78206</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>78206</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>78206</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>57930</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>57930</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>57930</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>78206</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>78206</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>78206</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3404</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7574</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>4530</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8837</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1869</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8523</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,58%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3404</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7439</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>54207</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>50037</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>56386</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>86,85%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>55271</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>50964</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>57849</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>51278</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>57932</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>92,42%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>85,22%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,74%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>54207</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>50172</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>56292</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>103691</t>
+          <t>104764</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113029</t>
+          <t>113484</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>57611</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>57611</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>57611</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>59801</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>59801</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>59801</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>57611</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>57611</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>57611</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7707,72 +7707,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3287</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5939</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>34,85%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>13,46%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>62,97%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2727</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5475</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5354</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>24,98%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>50,14%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3287</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1245</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5858</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>34,85%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -7820,72 +7820,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6145</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3493</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8162</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>65,15%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>37,03%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>86,54%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>8191</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>5443</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10200</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>5564</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>10234</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>75,02%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>49,86%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>93,43%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>6145</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>3574</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8187</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>65,15%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10755</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,84%</t>
         </is>
       </c>
     </row>
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9432</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9432</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>9432</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>10918</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>10918</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>10918</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>9432</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>9432</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>9432</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8055,67 +8055,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>16171</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>10391</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>24300</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>15016</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>9935</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>21708</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>9486</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>21906</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>7,66%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>16171</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>10631</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>23642</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23892</t>
+          <t>23635</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41408</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>212021</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>203892</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>217801</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>89,35%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>95,45%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>181009</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>174317</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>186090</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>174119</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>186539</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>92,34%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>88,93%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>212021</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>204550</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>217561</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>92,91%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>382808</t>
+          <t>383083</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>400324</t>
+          <t>400581</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>228192</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>228192</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>228192</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>299</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>196025</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>196025</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>196025</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>228192</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>228192</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>228192</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
